--- a/data/trans_bre/P2B_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2B_R-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,31; 10,28</t>
+          <t>-15,45; 9,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 4,48</t>
+          <t>-3,29; 3,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 12,24</t>
+          <t>-2,5; 11,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-23,28; 4,01</t>
+          <t>-23,21; 3,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-22,95; 19,85</t>
+          <t>-23,78; 19,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 4,75</t>
+          <t>-3,34; 4,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 15,14</t>
+          <t>-2,73; 13,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-38,5; 7,65</t>
+          <t>-37,67; 6,83</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 10,58</t>
+          <t>-5,27; 10,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 1,04</t>
+          <t>-10,34; 0,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 5,99</t>
+          <t>-7,79; 6,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-15,54; 2,82</t>
+          <t>-14,55; 1,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,12; 34,44</t>
+          <t>-13,81; 33,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-10,29; 1,04</t>
+          <t>-10,96; 0,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 7,74</t>
+          <t>-9,29; 7,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-33,61; 7,45</t>
+          <t>-32,78; 4,49</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 12,82</t>
+          <t>-7,71; 12,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,29; 8,64</t>
+          <t>-9,8; 9,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,79; 5,42</t>
+          <t>-13,08; 5,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 13,22</t>
+          <t>-4,35; 12,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-25,2; 57,56</t>
+          <t>-24,3; 57,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 11,99</t>
+          <t>-12,21; 13,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-19,37; 8,57</t>
+          <t>-18,56; 9,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,45; 54,21</t>
+          <t>-12,18; 52,15</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 9,03</t>
+          <t>-2,64; 9,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 13,01</t>
+          <t>-7,23; 13,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-13,49; 8,83</t>
+          <t>-12,53; 9,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,77; 3,4</t>
+          <t>-17,15; 2,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,57; 124,94</t>
+          <t>-23,33; 122,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-9,92; 21,68</t>
+          <t>-10,52; 22,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-28,46; 22,5</t>
+          <t>-26,31; 25,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-47,43; 14,37</t>
+          <t>-47,56; 10,84</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 5,27</t>
+          <t>-3,61; 5,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 2,61</t>
+          <t>-4,95; 2,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 2,75</t>
+          <t>-6,14; 2,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 1,95</t>
+          <t>-8,85; 1,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 18,98</t>
+          <t>-10,71; 21,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 3,13</t>
+          <t>-5,83; 3,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 4,09</t>
+          <t>-8,56; 4,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-25,79; 6,15</t>
+          <t>-24,84; 5,18</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2B_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2B_R-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,45; 9,96</t>
+          <t>-16,17; 9,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 3,95</t>
+          <t>-2,96; 4,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 11,31</t>
+          <t>-2,89; 11,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-23,21; 3,06</t>
+          <t>-24,24; 4,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-23,78; 19,29</t>
+          <t>-24,6; 17,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 4,16</t>
+          <t>-3,02; 4,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 13,92</t>
+          <t>-3,12; 14,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-37,67; 6,83</t>
+          <t>-39,6; 9,42</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 10,24</t>
+          <t>-5,88; 10,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 0,1</t>
+          <t>-10,01; 0,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 6,15</t>
+          <t>-7,04; 6,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,55; 1,68</t>
+          <t>-14,61; 2,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,81; 33,25</t>
+          <t>-15,45; 34,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 0,1</t>
+          <t>-10,7; 0,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 7,96</t>
+          <t>-8,35; 8,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-32,78; 4,49</t>
+          <t>-31,91; 5,46</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 12,87</t>
+          <t>-7,51; 12,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 9,98</t>
+          <t>-12,26; 8,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,08; 5,66</t>
+          <t>-13,31; 5,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 12,88</t>
+          <t>-4,16; 12,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-24,3; 57,38</t>
+          <t>-24,35; 53,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,21; 13,77</t>
+          <t>-14,84; 11,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-18,56; 9,15</t>
+          <t>-18,9; 9,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 52,15</t>
+          <t>-12,53; 51,85</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 9,15</t>
+          <t>-2,65; 9,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 13,29</t>
+          <t>-7,02; 12,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,53; 9,45</t>
+          <t>-12,25; 8,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-17,15; 2,73</t>
+          <t>-16,99; 3,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,33; 122,01</t>
+          <t>-21,84; 122,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 22,6</t>
+          <t>-10,2; 20,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-26,31; 25,28</t>
+          <t>-25,46; 22,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-47,56; 10,84</t>
+          <t>-47,05; 13,75</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 5,98</t>
+          <t>-2,73; 6,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 2,55</t>
+          <t>-4,89; 2,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 2,94</t>
+          <t>-6,41; 3,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 1,72</t>
+          <t>-8,76; 1,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,71; 21,73</t>
+          <t>-8,18; 21,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 3,13</t>
+          <t>-5,7; 3,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 4,51</t>
+          <t>-9,01; 4,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-24,84; 5,18</t>
+          <t>-23,91; 4,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2B_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2B_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-9,6</t>
+          <t>-11,14</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-17,76%</t>
+          <t>-20,72%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,17; 9,17</t>
+          <t>-14,31; 10,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 4,36</t>
+          <t>-3,09; 4,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 11,9</t>
+          <t>-2,69; 12,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-24,24; 4,76</t>
+          <t>-24,54; 2,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-24,6; 17,17</t>
+          <t>-22,95; 19,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 4,63</t>
+          <t>-3,15; 4,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 14,55</t>
+          <t>-2,97; 15,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-39,6; 9,42</t>
+          <t>-40,49; 5,33</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-6,56</t>
+          <t>-5,55</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-15,8%</t>
+          <t>-13,17%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 10,36</t>
+          <t>-5,04; 10,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,01; 0,77</t>
+          <t>-9,64; 1,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 6,48</t>
+          <t>-7,48; 5,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,61; 2,05</t>
+          <t>-14,4; 4,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-15,45; 34,28</t>
+          <t>-13,12; 34,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 0,75</t>
+          <t>-10,29; 1,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 8,52</t>
+          <t>-8,98; 7,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-31,91; 5,46</t>
+          <t>-31,15; 10,92</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,45</t>
+          <t>4,23</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 12,85</t>
+          <t>-8,79; 12,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,26; 8,19</t>
+          <t>-11,29; 8,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,31; 5,49</t>
+          <t>-13,79; 5,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 12,82</t>
+          <t>-4,33; 13,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-24,35; 53,2</t>
+          <t>-25,2; 57,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,84; 11,14</t>
+          <t>-14,0; 11,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-18,9; 9,03</t>
+          <t>-19,37; 8,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,53; 51,85</t>
+          <t>-12,39; 49,12</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-5,98</t>
+          <t>-6,22</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-20,06%</t>
+          <t>-19,82%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 9,41</t>
+          <t>-2,76; 9,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 12,17</t>
+          <t>-7,14; 13,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 8,07</t>
+          <t>-13,49; 8,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,99; 3,45</t>
+          <t>-14,37; 1,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,84; 122,25</t>
+          <t>-23,57; 124,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-10,2; 20,73</t>
+          <t>-9,92; 21,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-25,46; 22,47</t>
+          <t>-28,46; 22,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-47,05; 13,75</t>
+          <t>-40,27; 6,3</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-3,54</t>
+          <t>-3,23</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-10,31%</t>
+          <t>-9,11%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 6,0</t>
+          <t>-4,05; 5,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 2,97</t>
+          <t>-4,91; 2,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 3,07</t>
+          <t>-6,43; 2,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 1,48</t>
+          <t>-8,6; 1,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 21,65</t>
+          <t>-11,9; 18,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 3,7</t>
+          <t>-5,79; 3,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 4,61</t>
+          <t>-8,95; 4,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-23,91; 4,58</t>
+          <t>-22,56; 4,96</t>
         </is>
       </c>
     </row>
